--- a/astro-site/public/dl/fine-dining-checklist-templates/06-sommelier-wine-pairing-checklist.xlsx
+++ b/astro-site/public/dl/fine-dining-checklist-templates/06-sommelier-wine-pairing-checklist.xlsx
@@ -651,7 +651,7 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>▸ Pour per pairing glass (≈60–80 ml per course).</t>
+          <t>▸ Pour per pairing glass (≈2–2.5 fl oz (60–80 ml) per course).</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Course 1 — Snack: wine/drink selected, glass, temp., ml</t>
+          <t>Course 1 — Snack: wine/drink selected, glass, temp., oz</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Course 2 — Amuse-bouche: wine/drink, glass, temp., ml</t>
+          <t>Course 2 — Amuse-bouche: wine/drink, glass, temp., oz</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Course 3 — Cold appetizer: wine/drink, glass, temp., ml</t>
+          <t>Course 3 — Cold appetizer: wine/drink, glass, temp., oz</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Course 4 — Hot appetizer: wine/drink, glass, temp., ml</t>
+          <t>Course 4 — Hot appetizer: wine/drink, glass, temp., oz</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Course 5 — Fish: wine/drink, glass, temp., ml</t>
+          <t>Course 5 — Fish: wine/drink, glass, temp., oz</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Course 6 — Meat: wine/drink, glass, temp., ml</t>
+          <t>Course 6 — Meat: wine/drink, glass, temp., oz</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Course 7 — Pre-dessert: wine/drink, glass, temp., ml</t>
+          <t>Course 7 — Pre-dessert: wine/drink, glass, temp., oz</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Course 8 — Dessert: wine/drink, glass, temp., ml</t>
+          <t>Course 8 — Dessert: wine/drink, glass, temp., oz</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
